--- a/APPT/data/output/Final_Production_Plan_2026-01-14.xlsx
+++ b/APPT/data/output/Final_Production_Plan_2026-01-14.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="398">
   <si>
     <t>Production Line</t>
   </si>
@@ -109,12 +109,12 @@
     <t>910728783</t>
   </si>
   <si>
+    <t>910728860</t>
+  </si>
+  <si>
     <t>AUTO_2</t>
   </si>
   <si>
-    <t>910728860</t>
-  </si>
-  <si>
     <t>910730952</t>
   </si>
   <si>
@@ -136,27 +136,21 @@
     <t>910730972 + 910730971</t>
   </si>
   <si>
+    <t>910730950</t>
+  </si>
+  <si>
+    <t>910731102 + 910730963</t>
+  </si>
+  <si>
     <t>AUTO_3</t>
   </si>
   <si>
-    <t>910730950</t>
-  </si>
-  <si>
-    <t>910731102 + 910730963</t>
-  </si>
-  <si>
-    <t>910730943 + 910731293</t>
-  </si>
-  <si>
     <t>910731190</t>
   </si>
   <si>
     <t>910731147</t>
   </si>
   <si>
-    <t>910731168 + 910731221</t>
-  </si>
-  <si>
     <t>910731183</t>
   </si>
   <si>
@@ -187,9 +181,15 @@
     <t>910731057</t>
   </si>
   <si>
+    <t>910730943</t>
+  </si>
+  <si>
     <t>910730961</t>
   </si>
   <si>
+    <t>910731168</t>
+  </si>
+  <si>
     <t>910731220 + 910731319</t>
   </si>
   <si>
@@ -199,6 +199,12 @@
     <t>910731292</t>
   </si>
   <si>
+    <t>910731221</t>
+  </si>
+  <si>
+    <t>910731293</t>
+  </si>
+  <si>
     <t>80880903</t>
   </si>
   <si>
@@ -223,36 +229,36 @@
     <t>80880900</t>
   </si>
   <si>
+    <t>83900259</t>
+  </si>
+  <si>
+    <t>80879274</t>
+  </si>
+  <si>
+    <t>80879278</t>
+  </si>
+  <si>
+    <t>80841061</t>
+  </si>
+  <si>
+    <t>83900258</t>
+  </si>
+  <si>
+    <t>80880901</t>
+  </si>
+  <si>
+    <t>80841060</t>
+  </si>
+  <si>
     <t>80880914</t>
   </si>
   <si>
-    <t>83900259</t>
+    <t>80851522</t>
   </si>
   <si>
     <t>80880904</t>
   </si>
   <si>
-    <t>80879274</t>
-  </si>
-  <si>
-    <t>80879278</t>
-  </si>
-  <si>
-    <t>80841061</t>
-  </si>
-  <si>
-    <t>83900258</t>
-  </si>
-  <si>
-    <t>80880901</t>
-  </si>
-  <si>
-    <t>80841060</t>
-  </si>
-  <si>
-    <t>80851522</t>
-  </si>
-  <si>
     <t>80879275</t>
   </si>
   <si>
@@ -262,6 +268,12 @@
     <t>80879283</t>
   </si>
   <si>
+    <t>80880910</t>
+  </si>
+  <si>
+    <t>80880916</t>
+  </si>
+  <si>
     <t>H&amp;S SS</t>
   </si>
   <si>
@@ -304,103 +316,100 @@
     <t>PTN Silky Smooth Shampoo</t>
   </si>
   <si>
-    <t>CI492</t>
-  </si>
-  <si>
-    <t>CI493</t>
+    <t>CI496</t>
+  </si>
+  <si>
+    <t>CI497</t>
   </si>
   <si>
     <t>REP01-0114</t>
   </si>
   <si>
-    <t>CI496</t>
-  </si>
-  <si>
-    <t>CI497</t>
+    <t>CI500</t>
+  </si>
+  <si>
+    <t>CI501</t>
+  </si>
+  <si>
+    <t>CI502</t>
+  </si>
+  <si>
+    <t>CI503</t>
+  </si>
+  <si>
+    <t>REP02-0114</t>
+  </si>
+  <si>
+    <t>CI504</t>
+  </si>
+  <si>
+    <t>CI505</t>
+  </si>
+  <si>
+    <t>CI506</t>
+  </si>
+  <si>
+    <t>CI507</t>
+  </si>
+  <si>
+    <t>CI508</t>
+  </si>
+  <si>
+    <t>CI509</t>
+  </si>
+  <si>
+    <t>CI512</t>
+  </si>
+  <si>
+    <t>CI513</t>
+  </si>
+  <si>
+    <t>CI514</t>
+  </si>
+  <si>
+    <t>REP03-0114</t>
+  </si>
+  <si>
+    <t>CI516</t>
+  </si>
+  <si>
+    <t>CI517</t>
+  </si>
+  <si>
+    <t>CI519</t>
+  </si>
+  <si>
+    <t>CI520</t>
+  </si>
+  <si>
+    <t>CI521</t>
+  </si>
+  <si>
+    <t>CI523</t>
+  </si>
+  <si>
+    <t>CI524</t>
   </si>
   <si>
     <t>CI498</t>
   </si>
   <si>
-    <t>REP02-0114</t>
-  </si>
-  <si>
     <t>CI499</t>
   </si>
   <si>
-    <t>CI500</t>
-  </si>
-  <si>
-    <t>CI501</t>
-  </si>
-  <si>
-    <t>CI502</t>
-  </si>
-  <si>
-    <t>CI503</t>
-  </si>
-  <si>
-    <t>CI504</t>
-  </si>
-  <si>
-    <t>CI505</t>
-  </si>
-  <si>
-    <t>CI508</t>
-  </si>
-  <si>
-    <t>REP03-0114</t>
-  </si>
-  <si>
-    <t>CI509</t>
+    <t>CI511</t>
   </si>
   <si>
     <t>CI510</t>
   </si>
   <si>
-    <t>CI511</t>
-  </si>
-  <si>
-    <t>CI512</t>
-  </si>
-  <si>
-    <t>CI513</t>
-  </si>
-  <si>
-    <t>CI514</t>
+    <t>CI525</t>
   </si>
   <si>
     <t>CI515</t>
   </si>
   <si>
-    <t>CI516</t>
-  </si>
-  <si>
-    <t>CI517</t>
-  </si>
-  <si>
-    <t>CI519</t>
-  </si>
-  <si>
-    <t>CI520</t>
-  </si>
-  <si>
-    <t>CI494</t>
-  </si>
-  <si>
-    <t>CI495</t>
-  </si>
-  <si>
-    <t>CI507</t>
-  </si>
-  <si>
-    <t>CI506</t>
-  </si>
-  <si>
-    <t>CI521</t>
-  </si>
-  <si>
-    <t>CI524</t>
+    <t>CI528</t>
   </si>
   <si>
     <t>CI518</t>
@@ -409,7 +418,16 @@
     <t>CI522</t>
   </si>
   <si>
-    <t>CI523</t>
+    <t>CI526</t>
+  </si>
+  <si>
+    <t>CI527</t>
+  </si>
+  <si>
+    <t>CI529</t>
+  </si>
+  <si>
+    <t>CI530</t>
   </si>
   <si>
     <t>21422079</t>
@@ -484,19 +502,13 @@
     <t>HC Base Tank</t>
   </si>
   <si>
-    <t>TK#_13_# [Wash 20m] + TK#_18_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_22_# [Wash 20m] + TK#_21_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_4_# [Wash 20m] + TK#_12_# [Wash 20m]</t>
-  </si>
-  <si>
-    <t>TK#_4_# + TK#_12_#</t>
-  </si>
-  <si>
-    <t>TK#_13_# + TK#_23_#</t>
+    <t>TK#_10_# [Wash 20m] + TK#_23_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_12_# [Wash 20m]</t>
+  </si>
+  <si>
+    <t>TK#_19_# [Wash 20m]</t>
   </si>
   <si>
     <t>LOW: SLS</t>
@@ -958,10 +970,10 @@
     <t>2026-01-16 09:00</t>
   </si>
   <si>
-    <t>CI492: H&amp;S SS</t>
-  </si>
-  <si>
-    <t>CI493: H&amp;S Daily Clean Libra</t>
+    <t>CI496: H&amp;S SS</t>
+  </si>
+  <si>
+    <t>CI497: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>WASHOUT</t>
@@ -970,124 +982,121 @@
     <t>REP01-0114: HC BASE</t>
   </si>
   <si>
-    <t>CI496: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI497: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI498: H&amp;S Daily Clean Libra</t>
+    <t>CI500: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI501: H&amp;S Daily Cool Libra</t>
+  </si>
+  <si>
+    <t>CI502: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI503: H&amp;S Daily Cool Libra</t>
   </si>
   <si>
     <t>REP02-0114: HC BASE</t>
   </si>
   <si>
-    <t>CI499: H&amp;S Daily Cool Libra</t>
-  </si>
-  <si>
-    <t>CI500: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI501: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
-    <t>CI502: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI503: H&amp;S Daily Smooth Libra</t>
-  </si>
-  <si>
     <t>CI504: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI505: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI508: H&amp;S Daily Smooth Libra</t>
+    <t>CI505: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI506: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI507: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI508: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI509: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI512: H&amp;S Daily Smooth Libra</t>
+  </si>
+  <si>
+    <t>CI513: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI514: H&amp;S CM</t>
   </si>
   <si>
     <t>REP03-0114: HC BASE</t>
   </si>
   <si>
-    <t>CI509: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI510: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI511: H&amp;S CM</t>
-  </si>
-  <si>
-    <t>CI512: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI513: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI514: H&amp;S AHF</t>
-  </si>
-  <si>
-    <t>CI515: PTN  Hair Fall Control</t>
-  </si>
-  <si>
     <t>CI516: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
     <t>CI517: H&amp;S Daily Clean Libra</t>
   </si>
   <si>
-    <t>CI519: H&amp;S Daily Clean Libra</t>
-  </si>
-  <si>
-    <t>CI520: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI494: PTN HFC Conditioner</t>
+    <t>CI519: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI520: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI521: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI523: H&amp;S Daily Clean Libra</t>
+  </si>
+  <si>
+    <t>CI524: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI498: PTN HFC Conditioner</t>
   </si>
   <si>
     <t>COND WASH (60m)</t>
   </si>
   <si>
-    <t>CI495: H&amp;S Neem Libra</t>
-  </si>
-  <si>
-    <t>CI507: PTN HFC Conditioner</t>
-  </si>
-  <si>
-    <t>CI506: H&amp;S LF</t>
-  </si>
-  <si>
-    <t>CI521: PTN SS Conditioner</t>
-  </si>
-  <si>
-    <t>CI524: PTN HFC Conditioner</t>
-  </si>
-  <si>
-    <t>CI518: PTN Healthy Shine</t>
-  </si>
-  <si>
-    <t>CI522: PTN  Hair Fall Control</t>
-  </si>
-  <si>
-    <t>CI523: PTN Silky Smooth Shampoo</t>
-  </si>
-  <si>
-    <t>TK#_4_#</t>
+    <t>CI499: H&amp;S Neem Libra</t>
+  </si>
+  <si>
+    <t>CI511: PTN HFC Conditioner</t>
+  </si>
+  <si>
+    <t>CI510: H&amp;S LF</t>
+  </si>
+  <si>
+    <t>CI525: PTN SS Conditioner</t>
+  </si>
+  <si>
+    <t>CI515: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>CI528: PTN HFC Conditioner</t>
+  </si>
+  <si>
+    <t>CI518: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI522: PTN Healthy Shine</t>
+  </si>
+  <si>
+    <t>CI526: PTN  Hair Fall Control</t>
+  </si>
+  <si>
+    <t>CI527: PTN Silky Smooth Shampoo</t>
+  </si>
+  <si>
+    <t>CI529: H&amp;S AHF</t>
+  </si>
+  <si>
+    <t>CI530: H&amp;S CM</t>
+  </si>
+  <si>
+    <t>TK#_10_#</t>
   </si>
   <si>
     <t>TK#_12_#</t>
   </si>
   <si>
-    <t>TK#_13_#</t>
-  </si>
-  <si>
-    <t>TK#_18_#</t>
-  </si>
-  <si>
-    <t>TK#_21_#</t>
-  </si>
-  <si>
-    <t>TK#_22_#</t>
+    <t>TK#_19_#</t>
   </si>
   <si>
     <t>TK#_23_#</t>
@@ -1123,13 +1132,43 @@
     <t>2026-01-16 14:00</t>
   </si>
   <si>
-    <t>CI517: H&amp;S Daily Clean Libra | CI519: H&amp;S Daily Clean Libra</t>
+    <t>2026-01-16 14:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 15:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 15:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 16:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 16:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 17:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 17:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 18:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 18:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 19:00</t>
+  </si>
+  <si>
+    <t>2026-01-16 19:30</t>
+  </si>
+  <si>
+    <t>2026-01-16 20:00</t>
   </si>
   <si>
     <t>WASHOUT (20m)</t>
-  </si>
-  <si>
-    <t>CI512: H&amp;S Daily Clean Libra | CI515: PTN  Hair Fall Control</t>
   </si>
   <si>
     <t>Sr.No</t>
@@ -1536,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="21" width="15.7109375" customWidth="1"/>
@@ -1609,46 +1648,46 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I2">
         <v>4.5088</v>
       </c>
       <c r="J2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L2" s="2">
-        <v>46035.5</v>
+        <v>46035.57638888889</v>
       </c>
       <c r="M2">
         <v>90</v>
       </c>
       <c r="N2" s="2">
-        <v>46035.5625</v>
+        <v>46035.63888888889</v>
       </c>
       <c r="O2">
-        <v>1150</v>
+        <v>1040</v>
       </c>
       <c r="P2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q2" s="2">
         <v>46036.36111111111</v>
@@ -1657,7 +1696,7 @@
         <v>46036.55</v>
       </c>
       <c r="S2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1668,46 +1707,46 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I3">
         <v>4.4185</v>
       </c>
       <c r="J3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L3" s="2">
-        <v>46035.5625</v>
+        <v>46035.63888888889</v>
       </c>
       <c r="M3">
         <v>90</v>
       </c>
       <c r="N3" s="2">
-        <v>46035.625</v>
+        <v>46035.70138888889</v>
       </c>
       <c r="O3">
-        <v>1071</v>
+        <v>961</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q3" s="2">
         <v>46036.36875</v>
@@ -1716,7 +1755,7 @@
         <v>46036.55208333334</v>
       </c>
       <c r="S3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1727,46 +1766,46 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I4">
         <v>2.2948</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L4" s="2">
-        <v>46035.63888888889</v>
+        <v>46035.71527777778</v>
       </c>
       <c r="M4">
         <v>90</v>
       </c>
       <c r="N4" s="2">
-        <v>46035.70138888889</v>
+        <v>46035.77777777778</v>
       </c>
       <c r="O4">
-        <v>1070</v>
+        <v>960</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Q4" s="2">
         <v>46036.44444444445</v>
@@ -1775,7 +1814,7 @@
         <v>46036.48611111111</v>
       </c>
       <c r="S4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1786,46 +1825,46 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I5">
         <v>4.4185</v>
       </c>
       <c r="J5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L5" s="2">
-        <v>46035.71527777778</v>
+        <v>46035.79166666666</v>
       </c>
       <c r="M5">
         <v>90</v>
       </c>
       <c r="N5" s="2">
-        <v>46035.77777777778</v>
+        <v>46035.85416666666</v>
       </c>
       <c r="O5">
-        <v>1115</v>
+        <v>1005</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q5" s="2">
         <v>46036.55208333334</v>
@@ -1834,7 +1873,7 @@
         <v>46036.73611111111</v>
       </c>
       <c r="S5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1845,46 +1884,46 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I6">
         <v>4.4163</v>
       </c>
       <c r="J6" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L6" s="2">
-        <v>46035.77777777778</v>
+        <v>46035.85416666666</v>
       </c>
       <c r="M6">
         <v>90</v>
       </c>
       <c r="N6" s="2">
-        <v>46035.84027777778</v>
+        <v>46035.91666666666</v>
       </c>
       <c r="O6">
-        <v>1047</v>
+        <v>937</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q6" s="2">
         <v>46036.56736111111</v>
@@ -1893,7 +1932,7 @@
         <v>46036.78125</v>
       </c>
       <c r="S6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1904,46 +1943,46 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H7" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I7">
         <v>4.4185</v>
       </c>
       <c r="J7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K7" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L7" s="2">
-        <v>46035.84027777778</v>
+        <v>46035.91666666666</v>
       </c>
       <c r="M7">
         <v>90</v>
       </c>
       <c r="N7" s="2">
-        <v>46035.90277777778</v>
+        <v>46035.97916666666</v>
       </c>
       <c r="O7">
-        <v>1200</v>
+        <v>1090</v>
       </c>
       <c r="P7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q7" s="2">
         <v>46036.73611111111</v>
@@ -1952,125 +1991,125 @@
         <v>46036.91944444444</v>
       </c>
       <c r="S7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="G8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I8">
-        <v>2.2948</v>
+        <v>4.4163</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L8" s="2">
-        <v>46035.91666666666</v>
+        <v>46036.3125</v>
       </c>
       <c r="M8">
         <v>90</v>
       </c>
       <c r="N8" s="2">
-        <v>46035.97916666666</v>
+        <v>46036.375</v>
       </c>
       <c r="O8">
-        <v>1120</v>
+        <v>645</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q8" s="2">
-        <v>46036.75694444445</v>
+        <v>46036.82291666666</v>
       </c>
       <c r="R8" s="2">
-        <v>46036.79861111111</v>
+        <v>46037.03611111111</v>
       </c>
       <c r="S8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I9">
-        <v>4.4163</v>
+        <v>2.2948</v>
       </c>
       <c r="J9" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L9" s="2">
-        <v>46036.3125</v>
+        <v>46036.38888888889</v>
       </c>
       <c r="M9">
         <v>90</v>
       </c>
       <c r="N9" s="2">
-        <v>46036.375</v>
+        <v>46036.45138888889</v>
       </c>
       <c r="O9">
-        <v>645</v>
+        <v>550</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q9" s="2">
-        <v>46036.82291666666</v>
+        <v>46036.83333333334</v>
       </c>
       <c r="R9" s="2">
-        <v>46037.03611111111</v>
+        <v>46036.875</v>
       </c>
       <c r="S9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2081,46 +2120,46 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I10">
         <v>4.4185</v>
       </c>
       <c r="J10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K10" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L10" s="2">
-        <v>46036.375</v>
+        <v>46036.46527777778</v>
       </c>
       <c r="M10">
         <v>90</v>
       </c>
       <c r="N10" s="2">
-        <v>46036.4375</v>
+        <v>46036.52777777778</v>
       </c>
       <c r="O10">
-        <v>694</v>
+        <v>564</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q10" s="2">
         <v>46036.91944444444</v>
@@ -2129,7 +2168,7 @@
         <v>46037.10347222222</v>
       </c>
       <c r="S10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2140,46 +2179,46 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I11">
         <v>4.4185</v>
       </c>
       <c r="J11" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L11" s="2">
-        <v>46036.4375</v>
+        <v>46036.52777777778</v>
       </c>
       <c r="M11">
         <v>90</v>
       </c>
       <c r="N11" s="2">
-        <v>46036.5</v>
+        <v>46036.59027777778</v>
       </c>
       <c r="O11">
-        <v>772</v>
+        <v>642</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q11" s="2">
         <v>46037.03611111111</v>
@@ -2188,7 +2227,7 @@
         <v>46037.25</v>
       </c>
       <c r="S11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2199,46 +2238,46 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I12">
         <v>4.4185</v>
       </c>
       <c r="J12" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L12" s="2">
-        <v>46036.5</v>
+        <v>46036.59027777778</v>
       </c>
       <c r="M12">
         <v>90</v>
       </c>
       <c r="N12" s="2">
-        <v>46036.5625</v>
+        <v>46036.65277777778</v>
       </c>
       <c r="O12">
-        <v>779</v>
+        <v>649</v>
       </c>
       <c r="P12" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q12" s="2">
         <v>46037.10347222222</v>
@@ -2247,7 +2286,7 @@
         <v>46037.28680555556</v>
       </c>
       <c r="S12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2258,46 +2297,46 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I13">
         <v>4.4185</v>
       </c>
       <c r="J13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L13" s="2">
-        <v>46036.5625</v>
+        <v>46036.65277777778</v>
       </c>
       <c r="M13">
         <v>90</v>
       </c>
       <c r="N13" s="2">
-        <v>46036.625</v>
+        <v>46036.71527777778</v>
       </c>
       <c r="O13">
-        <v>900</v>
+        <v>770</v>
       </c>
       <c r="P13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q13" s="2">
         <v>46037.25</v>
@@ -2306,7 +2345,7 @@
         <v>46037.46319444444</v>
       </c>
       <c r="S13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2317,46 +2356,46 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G14" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I14">
         <v>4.4185</v>
       </c>
       <c r="J14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K14" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L14" s="2">
-        <v>46036.625</v>
+        <v>46036.71527777778</v>
       </c>
       <c r="M14">
         <v>90</v>
       </c>
       <c r="N14" s="2">
-        <v>46036.6875</v>
+        <v>46036.77777777778</v>
       </c>
       <c r="O14">
-        <v>863</v>
+        <v>733</v>
       </c>
       <c r="P14" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q14" s="2">
         <v>46037.28680555556</v>
@@ -2365,7 +2404,7 @@
         <v>46037.47083333333</v>
       </c>
       <c r="S14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2376,46 +2415,46 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H15" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I15">
         <v>4.4891</v>
       </c>
       <c r="J15" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L15" s="2">
-        <v>46036.6875</v>
+        <v>46036.77777777778</v>
       </c>
       <c r="M15">
         <v>90</v>
       </c>
       <c r="N15" s="2">
-        <v>46036.75</v>
+        <v>46036.84027777778</v>
       </c>
       <c r="O15">
-        <v>810</v>
+        <v>680</v>
       </c>
       <c r="P15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q15" s="2">
         <v>46037.3125</v>
@@ -2424,7 +2463,7 @@
         <v>46037.75833333333</v>
       </c>
       <c r="S15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2435,46 +2474,46 @@
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H16" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I16">
         <v>4.4163</v>
       </c>
       <c r="J16" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K16" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L16" s="2">
-        <v>46036.76388888889</v>
+        <v>46036.85416666666</v>
       </c>
       <c r="M16">
         <v>90</v>
       </c>
       <c r="N16" s="2">
-        <v>46036.82638888889</v>
+        <v>46036.91666666666</v>
       </c>
       <c r="O16">
-        <v>917</v>
+        <v>787</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q16" s="2">
         <v>46037.46319444444</v>
@@ -2483,479 +2522,479 @@
         <v>46037.67708333334</v>
       </c>
       <c r="S16" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I17">
-        <v>2.2948</v>
+        <v>4.4185</v>
       </c>
       <c r="J17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K17" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L17" s="2">
-        <v>46036.84027777778</v>
+        <v>46036.91666666666</v>
       </c>
       <c r="M17">
         <v>90</v>
       </c>
       <c r="N17" s="2">
-        <v>46036.90277777778</v>
+        <v>46036.97916666666</v>
       </c>
       <c r="O17">
-        <v>802</v>
+        <v>708</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="Q17" s="2">
-        <v>46037.45972222222</v>
+        <v>46037.47083333333</v>
       </c>
       <c r="R17" s="2">
-        <v>46037.50138888889</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="S17" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G18" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I18">
-        <v>4.4185</v>
+        <v>4.0957</v>
       </c>
       <c r="J18" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K18" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L18" s="2">
-        <v>46036.91666666666</v>
+        <v>46037.31597222222</v>
       </c>
       <c r="M18">
         <v>90</v>
       </c>
       <c r="N18" s="2">
-        <v>46036.97916666666</v>
+        <v>46037.37847222222</v>
       </c>
       <c r="O18">
-        <v>708</v>
+        <v>176</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q18" s="2">
-        <v>46037.47083333333</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="R18" s="2">
-        <v>46037.65486111111</v>
+        <v>46037.6375</v>
       </c>
       <c r="S18" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F19" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H19" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I19">
-        <v>4.0957</v>
+        <v>2.2948</v>
       </c>
       <c r="J19" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L19" s="2">
-        <v>46037.29305555556</v>
+        <v>46037.39236111111</v>
       </c>
       <c r="M19">
         <v>90</v>
       </c>
       <c r="N19" s="2">
-        <v>46037.35555555556</v>
+        <v>46037.45486111111</v>
       </c>
       <c r="O19">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q19" s="2">
-        <v>46037.50069444445</v>
+        <v>46037.59861111111</v>
       </c>
       <c r="R19" s="2">
-        <v>46037.6375</v>
+        <v>46037.64027777778</v>
       </c>
       <c r="S19" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I20">
-        <v>5.2051</v>
+        <v>4.4185</v>
       </c>
       <c r="J20" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L20" s="2">
-        <v>46037.35555555556</v>
+        <v>46037.46875</v>
       </c>
       <c r="M20">
         <v>90</v>
       </c>
       <c r="N20" s="2">
-        <v>46037.41805555556</v>
+        <v>46037.53125</v>
       </c>
       <c r="O20">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="P20" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q20" s="2">
-        <v>46037.6375</v>
+        <v>46037.65486111111</v>
       </c>
       <c r="R20" s="2">
-        <v>46038.77569444444</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="S20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I21">
-        <v>4.4185</v>
+        <v>4.4163</v>
       </c>
       <c r="J21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L21" s="2">
-        <v>46037.41805555556</v>
+        <v>46037.53125</v>
       </c>
       <c r="M21">
         <v>90</v>
       </c>
       <c r="N21" s="2">
-        <v>46037.48055555556</v>
+        <v>46037.59375</v>
       </c>
       <c r="O21">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="2">
-        <v>46037.65486111111</v>
+        <v>46037.67708333334</v>
       </c>
       <c r="R21" s="2">
-        <v>46037.83819444444</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="S21" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H22" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I22">
-        <v>4.4163</v>
+        <v>4.5228</v>
       </c>
       <c r="J22" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K22" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L22" s="2">
-        <v>46037.48055555556</v>
+        <v>46037.61944444444</v>
       </c>
       <c r="M22">
         <v>90</v>
       </c>
       <c r="N22" s="2">
-        <v>46037.54305555556</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="O22">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q22" s="2">
-        <v>46037.67708333334</v>
+        <v>46037.81805555556</v>
       </c>
       <c r="R22" s="2">
-        <v>46037.89027777778</v>
+        <v>46037.93819444445</v>
       </c>
       <c r="S22" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H23" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I23">
-        <v>5.2051</v>
+        <v>4.4185</v>
       </c>
       <c r="J23" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K23" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L23" s="2">
-        <v>46037.54305555556</v>
+        <v>46037.68194444444</v>
       </c>
       <c r="M23">
         <v>90</v>
       </c>
       <c r="N23" s="2">
-        <v>46037.60555555556</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="O23">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q23" s="2">
-        <v>46037.75833333333</v>
+        <v>46037.83819444444</v>
       </c>
       <c r="R23" s="2">
-        <v>46038.71527777778</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="S23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I24">
-        <v>4.5228</v>
+        <v>4.4163</v>
       </c>
       <c r="J24" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L24" s="2">
-        <v>46037.61944444444</v>
+        <v>46037.74444444444</v>
       </c>
       <c r="M24">
         <v>90</v>
       </c>
       <c r="N24" s="2">
-        <v>46037.68194444444</v>
+        <v>46037.80694444444</v>
       </c>
       <c r="O24">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q24" s="2">
-        <v>46037.81805555556</v>
+        <v>46037.89027777778</v>
       </c>
       <c r="R24" s="2">
-        <v>46037.93819444445</v>
+        <v>46038.10416666666</v>
       </c>
       <c r="S24" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2966,232 +3005,232 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H25" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I25">
         <v>4.4185</v>
       </c>
       <c r="J25" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L25" s="2">
-        <v>46037.68194444444</v>
+        <v>46037.87638888889</v>
       </c>
       <c r="M25">
         <v>90</v>
       </c>
       <c r="N25" s="2">
-        <v>46037.74444444444</v>
+        <v>46037.93888888889</v>
       </c>
       <c r="O25">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q25" s="2">
-        <v>46037.83819444444</v>
+        <v>46038.02222222222</v>
       </c>
       <c r="R25" s="2">
-        <v>46038.02222222222</v>
+        <v>46038.20555555556</v>
       </c>
       <c r="S25" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I26">
-        <v>4.4163</v>
+        <v>5.1635</v>
       </c>
       <c r="J26" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K26" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="L26" s="2">
-        <v>46037.74444444444</v>
+        <v>46038.23472222222</v>
       </c>
       <c r="M26">
         <v>90</v>
       </c>
       <c r="N26" s="2">
-        <v>46037.80694444444</v>
+        <v>46038.29722222222</v>
       </c>
       <c r="O26">
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q26" s="2">
-        <v>46037.89027777778</v>
+        <v>46038.38055555556</v>
       </c>
       <c r="R26" s="2">
-        <v>46038.10416666666</v>
+        <v>46038.53472222222</v>
       </c>
       <c r="S26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H27" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I27">
-        <v>4.4185</v>
+        <v>1.1202</v>
       </c>
       <c r="J27" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L27" s="2">
-        <v>46037.87638888889</v>
+        <v>46035.33333333334</v>
       </c>
       <c r="M27">
         <v>90</v>
       </c>
       <c r="N27" s="2">
-        <v>46037.93888888889</v>
+        <v>46035.39583333334</v>
       </c>
       <c r="O27">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="P27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q27" s="2">
-        <v>46038.02222222222</v>
+        <v>46036.39583333334</v>
       </c>
       <c r="R27" s="2">
-        <v>46038.20555555556</v>
+        <v>46037.41041666667</v>
       </c>
       <c r="S27" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I28">
-        <v>5.1635</v>
+        <v>2.2082</v>
       </c>
       <c r="J28" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K28" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L28" s="2">
-        <v>46038.23472222222</v>
+        <v>46035.4375</v>
       </c>
       <c r="M28">
         <v>90</v>
       </c>
       <c r="N28" s="2">
-        <v>46038.29722222222</v>
+        <v>46035.5</v>
       </c>
       <c r="O28">
-        <v>120</v>
+        <v>1384</v>
       </c>
       <c r="P28" t="s">
         <v>159</v>
       </c>
       <c r="Q28" s="2">
-        <v>46038.38055555556</v>
+        <v>46036.46111111111</v>
       </c>
       <c r="R28" s="2">
-        <v>46038.53472222222</v>
+        <v>46036.56736111111</v>
       </c>
       <c r="S28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3205,111 +3244,111 @@
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I29">
         <v>1.1202</v>
       </c>
       <c r="J29" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K29" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L29" s="2">
-        <v>46035.33333333334</v>
+        <v>46035.84791666667</v>
       </c>
       <c r="M29">
         <v>90</v>
       </c>
       <c r="N29" s="2">
-        <v>46035.39583333334</v>
+        <v>46035.91041666667</v>
       </c>
       <c r="O29">
-        <v>1440</v>
+        <v>2160</v>
       </c>
       <c r="P29" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q29" s="2">
-        <v>46036.39583333334</v>
+        <v>46037.41041666667</v>
       </c>
       <c r="R29" s="2">
-        <v>46037.41041666667</v>
+        <v>46038.42569444444</v>
       </c>
       <c r="S29" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
         <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H30" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I30">
-        <v>2.2082</v>
+        <v>2.2544</v>
       </c>
       <c r="J30" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K30" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L30" s="2">
-        <v>46035.4375</v>
+        <v>46036.34375</v>
       </c>
       <c r="M30">
         <v>90</v>
       </c>
       <c r="N30" s="2">
-        <v>46035.5</v>
+        <v>46036.40625</v>
       </c>
       <c r="O30">
-        <v>1384</v>
+        <v>1440</v>
       </c>
       <c r="P30" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q30" s="2">
-        <v>46036.46111111111</v>
+        <v>46037.40625</v>
       </c>
       <c r="R30" s="2">
-        <v>46036.56736111111</v>
+        <v>46037.50069444445</v>
       </c>
       <c r="S30" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3320,55 +3359,55 @@
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H31" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I31">
-        <v>1.1202</v>
+        <v>0.5601</v>
       </c>
       <c r="J31" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K31" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L31" s="2">
-        <v>46035.53472222222</v>
+        <v>46036.86319444444</v>
       </c>
       <c r="M31">
         <v>90</v>
       </c>
       <c r="N31" s="2">
-        <v>46035.59722222222</v>
+        <v>46036.92569444444</v>
       </c>
       <c r="O31">
-        <v>2611</v>
+        <v>2160</v>
       </c>
       <c r="P31" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q31" s="2">
-        <v>46037.41041666667</v>
+        <v>46038.42569444444</v>
       </c>
       <c r="R31" s="2">
-        <v>46038.42569444444</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="S31" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -3379,55 +3418,55 @@
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H32" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I32">
-        <v>2.2544</v>
+        <v>2.2614</v>
       </c>
       <c r="J32" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K32" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L32" s="2">
-        <v>46035.63888888889</v>
+        <v>46036.96736111111</v>
       </c>
       <c r="M32">
         <v>90</v>
       </c>
       <c r="N32" s="2">
-        <v>46035.70138888889</v>
+        <v>46037.02986111111</v>
       </c>
       <c r="O32">
-        <v>2455</v>
+        <v>875</v>
       </c>
       <c r="P32" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q32" s="2">
-        <v>46037.40625</v>
+        <v>46037.6375</v>
       </c>
       <c r="R32" s="2">
-        <v>46037.50069444445</v>
+        <v>46037.69791666666</v>
       </c>
       <c r="S32" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -3438,114 +3477,114 @@
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F33" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H33" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I33">
-        <v>0.5601</v>
+        <v>0.28</v>
       </c>
       <c r="J33" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K33" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L33" s="2">
-        <v>46036.36319444444</v>
+        <v>46037.3125</v>
       </c>
       <c r="M33">
         <v>90</v>
       </c>
       <c r="N33" s="2">
-        <v>46036.42569444444</v>
+        <v>46037.375</v>
       </c>
       <c r="O33">
-        <v>2880</v>
+        <v>1771</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q33" s="2">
-        <v>46038.42569444444</v>
+        <v>46038.60486111111</v>
       </c>
       <c r="R33" s="2">
-        <v>46038.60486111111</v>
+        <v>46039.42569444444</v>
       </c>
       <c r="S33" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H34" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I34">
-        <v>0.28</v>
+        <v>2.2614</v>
       </c>
       <c r="J34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="L34" s="2">
-        <v>46036.54236111111</v>
+        <v>46037.41666666666</v>
       </c>
       <c r="M34">
         <v>90</v>
       </c>
       <c r="N34" s="2">
-        <v>46036.60486111111</v>
+        <v>46037.47916666666</v>
       </c>
       <c r="O34">
-        <v>2880</v>
+        <v>402</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q34" s="2">
-        <v>46038.60486111111</v>
+        <v>46037.75833333333</v>
       </c>
       <c r="R34" s="2">
-        <v>46039.42569444444</v>
+        <v>46037.81805555556</v>
       </c>
       <c r="S34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -3556,46 +3595,46 @@
         <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I35">
         <v>2.2733</v>
       </c>
       <c r="J35" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K35" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L35" s="2">
-        <v>46036.64652777778</v>
+        <v>46037.49305555555</v>
       </c>
       <c r="M35">
         <v>90</v>
       </c>
       <c r="N35" s="2">
-        <v>46036.70902777778</v>
+        <v>46037.55555555555</v>
       </c>
       <c r="O35">
-        <v>1770</v>
+        <v>551</v>
       </c>
       <c r="P35" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q35" s="2">
         <v>46037.93819444445</v>
@@ -3604,7 +3643,7 @@
         <v>46038.38055555556</v>
       </c>
       <c r="S35" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -3615,46 +3654,46 @@
         <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F36" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H36" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I36">
         <v>2.2511</v>
       </c>
       <c r="J36" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K36" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L36" s="2">
-        <v>46036.72291666667</v>
+        <v>46037.56944444445</v>
       </c>
       <c r="M36">
         <v>90</v>
       </c>
       <c r="N36" s="2">
-        <v>46036.78541666667</v>
+        <v>46037.63194444445</v>
       </c>
       <c r="O36">
-        <v>2519</v>
+        <v>1300</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q36" s="2">
         <v>46038.53472222222</v>
@@ -3663,7 +3702,7 @@
         <v>46038.59513888889</v>
       </c>
       <c r="S36" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3674,46 +3713,46 @@
         <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E37" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G37" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H37" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I37">
         <v>2.2511</v>
       </c>
       <c r="J37" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K37" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L37" s="2">
-        <v>46036.79930555556</v>
+        <v>46037.64583333334</v>
       </c>
       <c r="M37">
         <v>90</v>
       </c>
       <c r="N37" s="2">
-        <v>46036.86180555556</v>
+        <v>46037.70833333334</v>
       </c>
       <c r="O37">
-        <v>2496</v>
+        <v>1277</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="Q37" s="2">
         <v>46038.59513888889</v>
@@ -3722,7 +3761,125 @@
         <v>46038.65555555555</v>
       </c>
       <c r="S37" t="s">
-        <v>160</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" t="s">
+        <v>135</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" t="s">
+        <v>151</v>
+      </c>
+      <c r="H38" t="s">
+        <v>152</v>
+      </c>
+      <c r="I38">
+        <v>2.2511</v>
+      </c>
+      <c r="J38" t="s">
+        <v>154</v>
+      </c>
+      <c r="K38" t="s">
+        <v>157</v>
+      </c>
+      <c r="L38" s="2">
+        <v>46037.72222222222</v>
+      </c>
+      <c r="M38">
+        <v>90</v>
+      </c>
+      <c r="N38" s="2">
+        <v>46037.78472222222</v>
+      </c>
+      <c r="O38">
+        <v>1254</v>
+      </c>
+      <c r="P38" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>46038.65555555555</v>
+      </c>
+      <c r="R38" s="2">
+        <v>46038.71527777778</v>
+      </c>
+      <c r="S38" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" t="s">
+        <v>142</v>
+      </c>
+      <c r="G39" t="s">
+        <v>151</v>
+      </c>
+      <c r="H39" t="s">
+        <v>152</v>
+      </c>
+      <c r="I39">
+        <v>2.2511</v>
+      </c>
+      <c r="J39" t="s">
+        <v>154</v>
+      </c>
+      <c r="K39" t="s">
+        <v>157</v>
+      </c>
+      <c r="L39" s="2">
+        <v>46037.79861111111</v>
+      </c>
+      <c r="M39">
+        <v>90</v>
+      </c>
+      <c r="N39" s="2">
+        <v>46037.86111111111</v>
+      </c>
+      <c r="O39">
+        <v>1230</v>
+      </c>
+      <c r="P39" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>46038.71527777778</v>
+      </c>
+      <c r="R39" s="2">
+        <v>46038.77569444444</v>
+      </c>
+      <c r="S39" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -3742,1567 +3899,1594 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>313</v>
+        <v>156</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>313</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>344</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>344</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B59" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B61" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>333</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>158</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>158</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B83" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>158</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>158</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>150</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>156</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>334</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>334</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
+        <v>334</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B102" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
+        <v>335</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B104" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
+        <v>319</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B105" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
+        <v>336</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+        <v>336</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+        <v>336</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>337</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
+        <v>337</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
+        <v>337</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B111" t="s">
-        <v>150</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
+        <v>156</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B112" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
+        <v>338</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B113" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
+        <v>338</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
+        <v>338</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
+        <v>339</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
+        <v>339</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
+        <v>339</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
+        <v>340</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
+        <v>340</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
+        <v>340</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B121" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
+        <v>157</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B122" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+        <v>157</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
+        <v>157</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B125" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B126" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B127" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B128" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B130" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B131" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B132" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B133" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B134" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B135" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B136" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B141" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -5312,883 +5496,833 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="9" width="25.7109375" style="3" customWidth="1"/>
+    <col min="3" max="6" width="25.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>299</v>
+      </c>
+      <c r="B19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>303</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>304</v>
+      </c>
+      <c r="B24" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>305</v>
+      </c>
+      <c r="B25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>308</v>
+      </c>
+      <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>311</v>
+      </c>
+      <c r="B31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>313</v>
+      </c>
+      <c r="B33" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>314</v>
+      </c>
+      <c r="B34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>315</v>
+      </c>
+      <c r="B35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>316</v>
+      </c>
+      <c r="B36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>361</v>
+      </c>
+      <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>363</v>
+      </c>
+      <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>364</v>
+      </c>
+      <c r="B40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>365</v>
+      </c>
+      <c r="B41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
         <v>369</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>272</v>
-      </c>
-      <c r="B6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="B45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
         <v>370</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>281</v>
-      </c>
-      <c r="B15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>284</v>
-      </c>
-      <c r="B18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>286</v>
-      </c>
-      <c r="B20" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>287</v>
-      </c>
-      <c r="B21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>289</v>
-      </c>
-      <c r="B23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>290</v>
-      </c>
-      <c r="B24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>292</v>
-      </c>
-      <c r="B26" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>293</v>
-      </c>
-      <c r="B27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>294</v>
-      </c>
-      <c r="B28" t="s">
-        <v>152</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>295</v>
-      </c>
-      <c r="B29" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>296</v>
-      </c>
-      <c r="B30" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>297</v>
-      </c>
-      <c r="B31" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>298</v>
-      </c>
-      <c r="B32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>299</v>
-      </c>
-      <c r="B33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>300</v>
-      </c>
-      <c r="B34" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>301</v>
-      </c>
-      <c r="B35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>302</v>
-      </c>
-      <c r="B36" t="s">
-        <v>152</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>303</v>
-      </c>
-      <c r="B37" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>304</v>
-      </c>
-      <c r="B38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>305</v>
-      </c>
-      <c r="B39" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>306</v>
-      </c>
-      <c r="B40" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>307</v>
-      </c>
-      <c r="B41" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>308</v>
-      </c>
-      <c r="B42" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>309</v>
-      </c>
-      <c r="B43" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>310</v>
-      </c>
-      <c r="B44" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>311</v>
-      </c>
-      <c r="B45" t="s">
-        <v>150</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>312</v>
-      </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>156</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>156</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>156</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>157</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>157</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+        <v>157</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>381</v>
+      </c>
+      <c r="B57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>382</v>
+      </c>
+      <c r="B58" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -6198,7 +6332,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -6208,34 +6342,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6243,25 +6377,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6269,25 +6403,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6295,25 +6429,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6321,25 +6455,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6347,25 +6481,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6373,25 +6507,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6399,25 +6533,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6425,25 +6559,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6451,25 +6585,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6477,25 +6611,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6503,25 +6637,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6529,25 +6663,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6555,25 +6689,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6581,25 +6715,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6607,25 +6741,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6633,25 +6767,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6659,25 +6793,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6685,25 +6819,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6711,25 +6845,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6737,25 +6871,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J21" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6763,25 +6897,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6789,25 +6923,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6815,25 +6949,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6841,25 +6975,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6867,25 +7001,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6893,25 +7027,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J27" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6919,25 +7053,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6945,22 +7079,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s">
         <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
         <v>73</v>
@@ -6971,25 +7105,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -6997,25 +7131,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -7023,13 +7157,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>91</v>
@@ -7038,10 +7172,10 @@
         <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -7049,25 +7183,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F33" t="s">
         <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -7075,25 +7209,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -7101,25 +7235,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -7127,25 +7261,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -7153,25 +7287,77 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J37" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>396</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>396</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" t="s">
+        <v>151</v>
+      </c>
+      <c r="J39" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
